--- a/Excel/day15.xlsx
+++ b/Excel/day15.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\data-analyst\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC75DC86-4CA7-4070-9F68-16B9A3F46D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB235CCE-4FEA-4E4F-BDE1-9EA6ED5B26F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2159DCA7-6F25-4124-8E1B-72A5B3FD8315}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{2159DCA7-6F25-4124-8E1B-72A5B3FD8315}"/>
   </bookViews>
   <sheets>
     <sheet name="Customers" sheetId="1" r:id="rId1"/>
     <sheet name="Orders" sheetId="3" r:id="rId2"/>
     <sheet name="categories" sheetId="5" r:id="rId3"/>
     <sheet name="Products" sheetId="2" r:id="rId4"/>
-    <sheet name="Order_items" sheetId="6" r:id="rId5"/>
-    <sheet name="Payments" sheetId="7" r:id="rId6"/>
-    <sheet name="Analysis" sheetId="4" r:id="rId7"/>
+    <sheet name="Sheet6" sheetId="13" r:id="rId5"/>
+    <sheet name="Order_items" sheetId="6" r:id="rId6"/>
+    <sheet name="Payments" sheetId="7" r:id="rId7"/>
+    <sheet name="Practice" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="tbl_categories">categories!$A$2:$B$6</definedName>
@@ -27,6 +28,9 @@
     <definedName name="tbl_products">Products!$A$2:$D$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="21" r:id="rId9"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -72,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="134">
   <si>
     <t>John</t>
   </si>
@@ -368,33 +372,6 @@
     <t>unit_price</t>
   </si>
   <si>
-    <t>1200.00</t>
-  </si>
-  <si>
-    <t>120.00</t>
-  </si>
-  <si>
-    <t>999.00</t>
-  </si>
-  <si>
-    <t>280.00</t>
-  </si>
-  <si>
-    <t>950.00</t>
-  </si>
-  <si>
-    <t>550.00</t>
-  </si>
-  <si>
-    <t>50.00</t>
-  </si>
-  <si>
-    <t>1100.00</t>
-  </si>
-  <si>
-    <t>530.00</t>
-  </si>
-  <si>
     <t>payment_id</t>
   </si>
   <si>
@@ -486,13 +463,28 @@
   </si>
   <si>
     <t>SEGMENT 2</t>
+  </si>
+  <si>
+    <t>Sum of quantity</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>revenue</t>
+  </si>
+  <si>
+    <t>Sum of revenue</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -627,30 +619,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -658,11 +650,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="22">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -675,54 +677,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </font>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -770,6 +724,9 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -945,47 +902,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
   </dxfs>
@@ -1001,6 +917,210 @@
 </styleSheet>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="User" refreshedDate="46208.179688657408" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="9" xr:uid="{3C5E26D2-31ED-4BA7-ABEF-99A338E9FEDD}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="tbl_order_items"/>
+  </cacheSource>
+  <cacheFields count="7">
+    <cacheField name="order_item_id" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="9"/>
+    </cacheField>
+    <cacheField name="order_id" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="8"/>
+    </cacheField>
+    <cacheField name="product_id" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="10"/>
+    </cacheField>
+    <cacheField name="quantity" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="2"/>
+    </cacheField>
+    <cacheField name="unit_price" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="50" maxValue="1200"/>
+    </cacheField>
+    <cacheField name="customer_id" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="6" count="6">
+        <n v="1"/>
+        <n v="2"/>
+        <n v="3"/>
+        <n v="4"/>
+        <n v="5"/>
+        <n v="6"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="revenue" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="100" maxValue="1200"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="9">
+  <r>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1200"/>
+    <x v="0"/>
+    <n v="1200"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="120"/>
+    <x v="0"/>
+    <n v="1200"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="999"/>
+    <x v="1"/>
+    <n v="999"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="7"/>
+    <n v="2"/>
+    <n v="280"/>
+    <x v="2"/>
+    <n v="560"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <n v="4"/>
+    <n v="4"/>
+    <n v="1"/>
+    <n v="950"/>
+    <x v="3"/>
+    <n v="950"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <n v="5"/>
+    <n v="9"/>
+    <n v="1"/>
+    <n v="550"/>
+    <x v="4"/>
+    <n v="550"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <n v="6"/>
+    <n v="6"/>
+    <n v="2"/>
+    <n v="50"/>
+    <x v="0"/>
+    <n v="100"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <n v="7"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="1100"/>
+    <x v="1"/>
+    <n v="1100"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <n v="8"/>
+    <n v="10"/>
+    <n v="1"/>
+    <n v="530"/>
+    <x v="5"/>
+    <n v="530"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EADBA829-E430-4C3A-89D3-272D1D289443}" name="PivotTable6" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:C10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sum of quantity" fld="3" baseField="0" baseItem="0"/>
+    <dataField name="Sum of revenue" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D63C3ACB-FF35-4AE1-AAFA-63E0EEE1EB10}" name="tbl_customers" displayName="tbl_customers" ref="A1:E40" totalsRowShown="0">
   <autoFilter ref="A1:E40" xr:uid="{D63C3ACB-FF35-4AE1-AAFA-63E0EEE1EB10}"/>
@@ -1012,14 +1132,14 @@
     <tableColumn id="2" xr3:uid="{31027205-E8B6-4DE9-BAEE-27237AFDD2B2}" name="first_name"/>
     <tableColumn id="3" xr3:uid="{B46BD0EC-2954-445C-8AB1-FD07D306C88C}" name="last_name"/>
     <tableColumn id="4" xr3:uid="{168CF27F-EA6B-4FFD-91D6-847DC8D38EEE}" name="city"/>
-    <tableColumn id="5" xr3:uid="{5EB5ACA4-E18F-4186-9AD9-85BACE33069E}" name="registration_date" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{5EB5ACA4-E18F-4186-9AD9-85BACE33069E}" name="registration_date" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C4B91C72-50F1-4522-9BFC-64393D6C790F}" name="tbl_product" displayName="tbl_product" ref="A1:D11" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21" tableBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C4B91C72-50F1-4522-9BFC-64393D6C790F}" name="tbl_product" displayName="tbl_product" ref="A1:D11" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19" tableBorderDxfId="18">
   <autoFilter ref="A1:D11" xr:uid="{C4B91C72-50F1-4522-9BFC-64393D6C790F}">
     <filterColumn colId="3">
       <customFilters>
@@ -1031,24 +1151,30 @@
     <sortCondition descending="1" ref="D1:D11"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{877B6033-23C5-4E07-95E6-A617AE530475}" name="product_id" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{0740371E-62EB-4A94-B820-1A4D4F39A087}" name="product_name" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{78F412A4-FFF1-4DDF-A5EF-C997FE6DF437}" name="category_id" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{CAA2FC7D-DB58-4018-A973-F6201E847F28}" name="price" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{877B6033-23C5-4E07-95E6-A617AE530475}" name="product_id" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{0740371E-62EB-4A94-B820-1A4D4F39A087}" name="product_name" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{78F412A4-FFF1-4DDF-A5EF-C997FE6DF437}" name="category_id" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{CAA2FC7D-DB58-4018-A973-F6201E847F28}" name="price" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{C810CF25-C79B-4B14-BC90-7E950200C5B3}" name="tbl_order_items" displayName="tbl_order_items" ref="A1:E10" totalsRowShown="0">
-  <autoFilter ref="A1:E10" xr:uid="{C810CF25-C79B-4B14-BC90-7E950200C5B3}"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{C810CF25-C79B-4B14-BC90-7E950200C5B3}" name="tbl_order_items" displayName="tbl_order_items" ref="A1:G10" totalsRowShown="0">
+  <autoFilter ref="A1:G10" xr:uid="{C810CF25-C79B-4B14-BC90-7E950200C5B3}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{A072B75B-2744-450D-A6EC-CE17D4D90DD2}" name="order_item_id"/>
     <tableColumn id="2" xr3:uid="{98CEE4CA-1B53-4871-93F7-CF260B754934}" name="order_id"/>
     <tableColumn id="3" xr3:uid="{1382BB4C-EF64-4113-8694-F4FD2E93BBAA}" name="product_id"/>
     <tableColumn id="4" xr3:uid="{4C7AE0EE-03B0-400B-BBA2-234C13BE3FEE}" name="quantity"/>
-    <tableColumn id="5" xr3:uid="{60E594F5-1094-4098-8CDC-A0BBECF69508}" name="unit_price"/>
+    <tableColumn id="5" xr3:uid="{60E594F5-1094-4098-8CDC-A0BBECF69508}" name="unit_price" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{7B7E544F-AC3D-43BF-BB4B-72D1C3D8DE87}" name="customer_id">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(B2,Orders!A:A,Orders!B:B)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{8AFDDA71-597B-46F3-863D-394283BAA6E5}" name="revenue">
+      <calculatedColumnFormula>D2*E2</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1062,30 +1188,30 @@
     <tableColumn id="2" xr3:uid="{E28903FD-7F7C-4922-8C64-420754DB282C}" name="order_id"/>
     <tableColumn id="3" xr3:uid="{7B9081FF-094C-4A53-A425-74D2CAF20750}" name="payment_method"/>
     <tableColumn id="4" xr3:uid="{A6BD7005-4A7B-4A3A-9FBE-746BC661E337}" name="payment_status"/>
-    <tableColumn id="5" xr3:uid="{6A567B63-6BA8-439B-B945-1681445DA43D}" name="payment_date" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{6A567B63-6BA8-439B-B945-1681445DA43D}" name="payment_date" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{A81E4264-AF61-4FDC-A513-02195349C5F9}" name="tbl_analysis" displayName="tbl_analysis" ref="A1:I5" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{A81E4264-AF61-4FDC-A513-02195349C5F9}" name="tbl_analysis" displayName="tbl_analysis" ref="A1:I5" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="A1:I5" xr:uid="{A81E4264-AF61-4FDC-A513-02195349C5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I5">
     <sortCondition descending="1" ref="B1:B5"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{06D632E4-D168-4E85-8DC5-624067BEE3DD}" name="Customer" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{DB0FC619-C853-4743-ABC3-7F7A68593EF0}" name="Revenue" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{F08AD2FD-BDC9-4B17-BFDB-DCE1A24E15C1}" name="SUM" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{0C463496-1B54-41F0-859F-E7D13EF0E315}" name="AVG" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{9D6981BA-A2CF-4A7F-BCD5-07EBD2068879}" name="MAX" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{F989309A-37C0-426C-A276-3C208D41BCC2}" name="MIN" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{861485A9-7006-4413-B280-954CD72B7DA8}" name="COUNT" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{70AFB3C9-32B3-4818-9F62-E932BB6412E6}" name="SEGMENT" dataDxfId="7">
+    <tableColumn id="1" xr3:uid="{06D632E4-D168-4E85-8DC5-624067BEE3DD}" name="Customer" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{DB0FC619-C853-4743-ABC3-7F7A68593EF0}" name="Revenue" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{F08AD2FD-BDC9-4B17-BFDB-DCE1A24E15C1}" name="SUM" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{0C463496-1B54-41F0-859F-E7D13EF0E315}" name="AVG" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{9D6981BA-A2CF-4A7F-BCD5-07EBD2068879}" name="MAX" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{F989309A-37C0-426C-A276-3C208D41BCC2}" name="MIN" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{861485A9-7006-4413-B280-954CD72B7DA8}" name="COUNT" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{70AFB3C9-32B3-4818-9F62-E932BB6412E6}" name="SEGMENT" dataDxfId="3">
       <calculatedColumnFormula>IF(B2&gt;1000,"VIP","Regular")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{082F2BEB-4294-48CB-8179-37E68E8A63E7}" name="SEGMENT 2" dataDxfId="6">
+    <tableColumn id="9" xr3:uid="{082F2BEB-4294-48CB-8179-37E68E8A63E7}" name="SEGMENT 2" dataDxfId="2">
       <calculatedColumnFormula array="1">_xlfn.IFS(B2&gt;1500,"Premium",B2&gt;1000,"VIP",TRUE,"Regular")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1411,16 +1537,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFFDD09F-A6F3-4D38-9726-720109F9878B}">
   <dimension ref="A1:E40"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.625" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="11.625" customWidth="1"/>
-    <col min="5" max="5" width="17.875" customWidth="1"/>
-    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>70</v>
       </c>
@@ -1437,7 +1563,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>39</v>
       </c>
@@ -1454,7 +1580,7 @@
         <v>45313</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>38</v>
       </c>
@@ -1471,7 +1597,7 @@
         <v>45311</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>37</v>
       </c>
@@ -1488,7 +1614,7 @@
         <v>45308</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>36</v>
       </c>
@@ -1505,7 +1631,7 @@
         <v>45306</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>35</v>
       </c>
@@ -1522,7 +1648,7 @@
         <v>45305</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>34</v>
       </c>
@@ -1539,7 +1665,7 @@
         <v>45303</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>33</v>
       </c>
@@ -1556,7 +1682,7 @@
         <v>45301</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>32</v>
       </c>
@@ -1573,7 +1699,7 @@
         <v>45298</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>31</v>
       </c>
@@ -1590,7 +1716,7 @@
         <v>45296</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>30</v>
       </c>
@@ -1607,7 +1733,7 @@
         <v>45029</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>29</v>
       </c>
@@ -1624,7 +1750,7 @@
         <v>45026</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>28</v>
       </c>
@@ -1641,7 +1767,7 @@
         <v>45024</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>27</v>
       </c>
@@ -1658,7 +1784,7 @@
         <v>45020</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26</v>
       </c>
@@ -1675,7 +1801,7 @@
         <v>45017</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>25</v>
       </c>
@@ -1692,7 +1818,7 @@
         <v>45013</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>24</v>
       </c>
@@ -1709,7 +1835,7 @@
         <v>45010</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>23</v>
       </c>
@@ -1726,7 +1852,7 @@
         <v>45007</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>22</v>
       </c>
@@ -1743,7 +1869,7 @@
         <v>45005</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>21</v>
       </c>
@@ -1760,7 +1886,7 @@
         <v>45003</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1777,7 +1903,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -1794,7 +1920,7 @@
         <v>44997</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>18</v>
       </c>
@@ -1811,7 +1937,7 @@
         <v>44995</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>17</v>
       </c>
@@ -1828,7 +1954,7 @@
         <v>44992</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>16</v>
       </c>
@@ -1845,7 +1971,7 @@
         <v>44988</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>15</v>
       </c>
@@ -1862,7 +1988,7 @@
         <v>44986</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>14</v>
       </c>
@@ -1879,7 +2005,7 @@
         <v>44982</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>13</v>
       </c>
@@ -1896,7 +2022,7 @@
         <v>44979</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>12</v>
       </c>
@@ -1913,7 +2039,7 @@
         <v>44977</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>11</v>
       </c>
@@ -1930,7 +2056,7 @@
         <v>44975</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>10</v>
       </c>
@@ -1947,7 +2073,7 @@
         <v>44971</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9</v>
       </c>
@@ -1964,7 +2090,7 @@
         <v>44968</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>8</v>
       </c>
@@ -1981,7 +2107,7 @@
         <v>44964</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>7</v>
       </c>
@@ -1998,7 +2124,7 @@
         <v>44962</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>6</v>
       </c>
@@ -2015,7 +2141,7 @@
         <v>44958</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>5</v>
       </c>
@@ -2032,7 +2158,7 @@
         <v>44954</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>4</v>
       </c>
@@ -2049,7 +2175,7 @@
         <v>44949</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>3</v>
       </c>
@@ -2066,7 +2192,7 @@
         <v>44947</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2</v>
       </c>
@@ -2083,7 +2209,7 @@
         <v>44944</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>1</v>
       </c>
@@ -2110,16 +2236,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82391712-F19A-4BE3-8E70-CFEDBBF80F35}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:R9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.25" customWidth="1"/>
-    <col min="2" max="2" width="13.625" customWidth="1"/>
-    <col min="3" max="3" width="12.5" customWidth="1"/>
-    <col min="5" max="5" width="9.25" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" customWidth="1"/>
+    <col min="13" max="13" width="11.5703125" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" customWidth="1"/>
+    <col min="17" max="17" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>75</v>
       </c>
@@ -2135,8 +2268,29 @@
       <c r="E1" s="8" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="H1" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="L1" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="M1" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="N1" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="R1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>6</v>
       </c>
@@ -2152,8 +2306,32 @@
       <c r="E2" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="H2" t="str">
+        <f>_xlfn.XLOOKUP(B2,tbl_customers[customer_id],tbl_customers[first_name])</f>
+        <v>John</v>
+      </c>
+      <c r="I2" t="str">
+        <f>_xlfn.XLOOKUP(B2,tbl_customers[customer_id],tbl_customers[last_name])</f>
+        <v>Smith</v>
+      </c>
+      <c r="J2" t="str">
+        <f>_xlfn.XLOOKUP(B2,tbl_customers[customer_id],tbl_customers[city])</f>
+        <v>New York</v>
+      </c>
+      <c r="L2" t="str">
+        <f>VLOOKUP(B2,Customers!A:D,2,FALSE)</f>
+        <v>John</v>
+      </c>
+      <c r="M2" t="str">
+        <f>VLOOKUP(B2,Customers!A:D,3,FALSE)</f>
+        <v>Smith</v>
+      </c>
+      <c r="N2" t="str">
+        <f>VLOOKUP(B2,Customers!A:D,4,FALSE)</f>
+        <v>New York</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>7</v>
       </c>
@@ -2169,8 +2347,32 @@
       <c r="E3" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="H3" t="str">
+        <f>_xlfn.XLOOKUP(B3,tbl_customers[customer_id],tbl_customers[first_name])</f>
+        <v>Emma</v>
+      </c>
+      <c r="I3" t="str">
+        <f>_xlfn.XLOOKUP(B3,tbl_customers[customer_id],tbl_customers[last_name])</f>
+        <v>Johnson</v>
+      </c>
+      <c r="J3" t="str">
+        <f>_xlfn.XLOOKUP(B3,tbl_customers[customer_id],tbl_customers[city])</f>
+        <v>Chicago</v>
+      </c>
+      <c r="L3" t="str">
+        <f>VLOOKUP(B3,Customers!A:D,2,FALSE)</f>
+        <v>Emma</v>
+      </c>
+      <c r="M3" t="str">
+        <f>VLOOKUP(B3,Customers!A:D,3,FALSE)</f>
+        <v>Johnson</v>
+      </c>
+      <c r="N3" t="str">
+        <f>VLOOKUP(B3,Customers!A:D,4,FALSE)</f>
+        <v>Chicago</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>8</v>
       </c>
@@ -2186,8 +2388,32 @@
       <c r="E4" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="H4" t="str">
+        <f>_xlfn.XLOOKUP(B4,tbl_customers[customer_id],tbl_customers[first_name])</f>
+        <v>Olivia</v>
+      </c>
+      <c r="I4" t="str">
+        <f>_xlfn.XLOOKUP(B4,tbl_customers[customer_id],tbl_customers[last_name])</f>
+        <v>Wilson</v>
+      </c>
+      <c r="J4" t="str">
+        <f>_xlfn.XLOOKUP(B4,tbl_customers[customer_id],tbl_customers[city])</f>
+        <v>Dallas</v>
+      </c>
+      <c r="L4" t="str">
+        <f>VLOOKUP(B4,Customers!A:D,2,FALSE)</f>
+        <v>Olivia</v>
+      </c>
+      <c r="M4" t="str">
+        <f>VLOOKUP(B4,Customers!A:D,3,FALSE)</f>
+        <v>Wilson</v>
+      </c>
+      <c r="N4" t="str">
+        <f>VLOOKUP(B4,Customers!A:D,4,FALSE)</f>
+        <v>Dallas</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>1</v>
       </c>
@@ -2203,8 +2429,32 @@
       <c r="E5" s="12" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="H5" t="str">
+        <f>_xlfn.XLOOKUP(B5,tbl_customers[customer_id],tbl_customers[first_name])</f>
+        <v>John</v>
+      </c>
+      <c r="I5" t="str">
+        <f>_xlfn.XLOOKUP(B5,tbl_customers[customer_id],tbl_customers[last_name])</f>
+        <v>Smith</v>
+      </c>
+      <c r="J5" t="str">
+        <f>_xlfn.XLOOKUP(B5,tbl_customers[customer_id],tbl_customers[city])</f>
+        <v>New York</v>
+      </c>
+      <c r="L5" t="str">
+        <f>VLOOKUP(B5,Customers!A:D,2,FALSE)</f>
+        <v>John</v>
+      </c>
+      <c r="M5" t="str">
+        <f>VLOOKUP(B5,Customers!A:D,3,FALSE)</f>
+        <v>Smith</v>
+      </c>
+      <c r="N5" t="str">
+        <f>VLOOKUP(B5,Customers!A:D,4,FALSE)</f>
+        <v>New York</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>2</v>
       </c>
@@ -2220,8 +2470,32 @@
       <c r="E6" s="10" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="H6" t="str">
+        <f>_xlfn.XLOOKUP(B6,tbl_customers[customer_id],tbl_customers[first_name])</f>
+        <v>Emma</v>
+      </c>
+      <c r="I6" t="str">
+        <f>_xlfn.XLOOKUP(B6,tbl_customers[customer_id],tbl_customers[last_name])</f>
+        <v>Johnson</v>
+      </c>
+      <c r="J6" t="str">
+        <f>_xlfn.XLOOKUP(B6,tbl_customers[customer_id],tbl_customers[city])</f>
+        <v>Chicago</v>
+      </c>
+      <c r="L6" t="str">
+        <f>VLOOKUP(B6,Customers!A:D,2,FALSE)</f>
+        <v>Emma</v>
+      </c>
+      <c r="M6" t="str">
+        <f>VLOOKUP(B6,Customers!A:D,3,FALSE)</f>
+        <v>Johnson</v>
+      </c>
+      <c r="N6" t="str">
+        <f>VLOOKUP(B6,Customers!A:D,4,FALSE)</f>
+        <v>Chicago</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>3</v>
       </c>
@@ -2237,8 +2511,32 @@
       <c r="E7" s="12" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="H7" t="str">
+        <f>_xlfn.XLOOKUP(B7,tbl_customers[customer_id],tbl_customers[first_name])</f>
+        <v>Michael</v>
+      </c>
+      <c r="I7" t="str">
+        <f>_xlfn.XLOOKUP(B7,tbl_customers[customer_id],tbl_customers[last_name])</f>
+        <v>Brown</v>
+      </c>
+      <c r="J7" t="str">
+        <f>_xlfn.XLOOKUP(B7,tbl_customers[customer_id],tbl_customers[city])</f>
+        <v>Los Angeles</v>
+      </c>
+      <c r="L7" t="str">
+        <f>VLOOKUP(B7,Customers!A:D,2,FALSE)</f>
+        <v>Michael</v>
+      </c>
+      <c r="M7" t="str">
+        <f>VLOOKUP(B7,Customers!A:D,3,FALSE)</f>
+        <v>Brown</v>
+      </c>
+      <c r="N7" t="str">
+        <f>VLOOKUP(B7,Customers!A:D,4,FALSE)</f>
+        <v>Los Angeles</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>4</v>
       </c>
@@ -2254,8 +2552,32 @@
       <c r="E8" s="10" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="H8" t="str">
+        <f>_xlfn.XLOOKUP(B8,tbl_customers[customer_id],tbl_customers[first_name])</f>
+        <v>Sophia</v>
+      </c>
+      <c r="I8" t="str">
+        <f>_xlfn.XLOOKUP(B8,tbl_customers[customer_id],tbl_customers[last_name])</f>
+        <v>Davis</v>
+      </c>
+      <c r="J8" t="str">
+        <f>_xlfn.XLOOKUP(B8,tbl_customers[customer_id],tbl_customers[city])</f>
+        <v>Houston</v>
+      </c>
+      <c r="L8" t="str">
+        <f>VLOOKUP(B8,Customers!A:D,2,FALSE)</f>
+        <v>Sophia</v>
+      </c>
+      <c r="M8" t="str">
+        <f>VLOOKUP(B8,Customers!A:D,3,FALSE)</f>
+        <v>Davis</v>
+      </c>
+      <c r="N8" t="str">
+        <f>VLOOKUP(B8,Customers!A:D,4,FALSE)</f>
+        <v>Houston</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -2270,6 +2592,30 @@
       </c>
       <c r="E9" s="6" t="s">
         <v>86</v>
+      </c>
+      <c r="H9" t="str">
+        <f>_xlfn.XLOOKUP(B9,tbl_customers[customer_id],tbl_customers[first_name])</f>
+        <v>Daniel</v>
+      </c>
+      <c r="I9" t="str">
+        <f>_xlfn.XLOOKUP(B9,tbl_customers[customer_id],tbl_customers[last_name])</f>
+        <v>Miller</v>
+      </c>
+      <c r="J9" t="str">
+        <f>_xlfn.XLOOKUP(B9,tbl_customers[customer_id],tbl_customers[city])</f>
+        <v>Phoenix</v>
+      </c>
+      <c r="L9" t="str">
+        <f>VLOOKUP(B9,Customers!A:D,2,FALSE)</f>
+        <v>Daniel</v>
+      </c>
+      <c r="M9" t="str">
+        <f>VLOOKUP(B9,Customers!A:D,3,FALSE)</f>
+        <v>Miller</v>
+      </c>
+      <c r="N9" t="str">
+        <f>VLOOKUP(B9,Customers!A:D,4,FALSE)</f>
+        <v>Phoenix</v>
       </c>
     </row>
   </sheetData>
@@ -2280,13 +2626,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A962695D-EF39-49E1-B55C-4EAEDFD1D99D}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="16.125" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>87</v>
       </c>
@@ -2294,7 +2640,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -2302,7 +2648,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>2</v>
       </c>
@@ -2310,7 +2656,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -2318,7 +2664,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>4</v>
       </c>
@@ -2326,7 +2672,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2342,33 +2688,33 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C690B74-47AB-4D23-B399-17FA8FA8069B}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.25" customWidth="1"/>
-    <col min="2" max="2" width="15.375" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>95</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C1" s="19" t="s">
         <v>87</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
         <v>1</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C2" s="14">
         <v>1</v>
@@ -2377,12 +2723,12 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="16">
         <v>2</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C3" s="16">
         <v>1</v>
@@ -2391,12 +2737,12 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
         <v>3</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C4" s="14">
         <v>2</v>
@@ -2405,12 +2751,12 @@
         <v>990</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <v>4</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C5" s="16">
         <v>2</v>
@@ -2419,12 +2765,12 @@
         <v>950</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>9</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C6" s="14">
         <v>5</v>
@@ -2433,12 +2779,12 @@
         <v>550</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <v>10</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C7" s="16">
         <v>5</v>
@@ -2447,12 +2793,12 @@
         <v>530</v>
       </c>
     </row>
-    <row r="8" spans="1:4" hidden="1">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <v>8</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C8" s="16">
         <v>4</v>
@@ -2461,12 +2807,12 @@
         <v>450</v>
       </c>
     </row>
-    <row r="9" spans="1:4" hidden="1">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>7</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C9" s="14">
         <v>4</v>
@@ -2475,12 +2821,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="10" spans="1:4" hidden="1">
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>5</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C10" s="14">
         <v>3</v>
@@ -2489,12 +2835,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:4" hidden="1">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <v>6</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C11" s="16">
         <v>3</v>
@@ -2503,7 +2849,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D12" s="23"/>
     </row>
   </sheetData>
@@ -2516,18 +2862,129 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3285F0B-A512-4695-A163-0F934B1A0BB6}">
+  <dimension ref="A3:C10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="29">
+        <v>1</v>
+      </c>
+      <c r="B4" s="27">
+        <v>4</v>
+      </c>
+      <c r="C4" s="27">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="29">
+        <v>2</v>
+      </c>
+      <c r="B5" s="27">
+        <v>2</v>
+      </c>
+      <c r="C5" s="27">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="29">
+        <v>3</v>
+      </c>
+      <c r="B6" s="27">
+        <v>2</v>
+      </c>
+      <c r="C6" s="27">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="29">
+        <v>4</v>
+      </c>
+      <c r="B7" s="27">
+        <v>1</v>
+      </c>
+      <c r="C7" s="27">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="29">
+        <v>5</v>
+      </c>
+      <c r="B8" s="27">
+        <v>1</v>
+      </c>
+      <c r="C8" s="27">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="29">
+        <v>6</v>
+      </c>
+      <c r="B9" s="27">
+        <v>1</v>
+      </c>
+      <c r="C9" s="27">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" s="27">
+        <v>11</v>
+      </c>
+      <c r="C10" s="27">
+        <v>7189</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1F1007-BEC2-432D-A92F-2EFB0EE6F026}">
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:R10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="10.25" customWidth="1"/>
-    <col min="3" max="3" width="12.25" customWidth="1"/>
-    <col min="4" max="4" width="9.75" customWidth="1"/>
-    <col min="5" max="5" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" customWidth="1"/>
+    <col min="8" max="8" width="23.140625" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" customWidth="1"/>
+    <col min="12" max="12" width="20.5703125" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" customWidth="1"/>
+    <col min="16" max="16" width="21.140625" customWidth="1"/>
+    <col min="17" max="17" width="11.5703125" customWidth="1"/>
+    <col min="18" max="18" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>94</v>
       </c>
@@ -2540,11 +2997,44 @@
       <c r="D1" t="s">
         <v>96</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="23" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P1" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2557,11 +3047,55 @@
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="E2" s="23">
+        <v>1200</v>
+      </c>
+      <c r="F2">
+        <f>_xlfn.XLOOKUP(B2,Orders!A:A,Orders!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="G2" s="23">
+        <f>D2*E2</f>
+        <v>1200</v>
+      </c>
+      <c r="H2" t="str">
+        <f>_xlfn.XLOOKUP(C2,tbl_product[product_id],tbl_product[product_name])</f>
+        <v>MacBook Air M3</v>
+      </c>
+      <c r="I2">
+        <f>_xlfn.XLOOKUP(C2,tbl_product[product_id],tbl_product[price])</f>
+        <v>1200</v>
+      </c>
+      <c r="J2">
+        <f>_xlfn.XLOOKUP(C2,tbl_product[product_id],tbl_product[category_id])</f>
+        <v>1</v>
+      </c>
+      <c r="L2" t="str">
+        <f>VLOOKUP(C2,Products!A:D,2,FALSE)</f>
+        <v>MacBook Air M3</v>
+      </c>
+      <c r="M2">
+        <f>VLOOKUP(C2,Products!A:D,4,FALSE)</f>
+        <v>1200</v>
+      </c>
+      <c r="N2">
+        <f>VLOOKUP(C2,Products!A:D,3,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="P2" t="str">
+        <f>INDEX(Products!B:B,MATCH(C2,Products!A:A,0))</f>
+        <v>MacBook Air M3</v>
+      </c>
+      <c r="Q2">
+        <f>INDEX(Products!D:D,MATCH(C2,Products!A:A,0))</f>
+        <v>1200</v>
+      </c>
+      <c r="R2">
+        <f>INDEX(Products!C:C,MATCH(C2,Products!A:A,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2574,11 +3108,55 @@
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="E3" s="23">
+        <v>120</v>
+      </c>
+      <c r="F3">
+        <f>_xlfn.XLOOKUP(B3,Orders!A:A,Orders!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <f>--D2*--E2</f>
+        <v>1200</v>
+      </c>
+      <c r="H3" t="str">
+        <f>_xlfn.XLOOKUP(C3,tbl_product[product_id],tbl_product[product_name])</f>
+        <v>Mechanical Keyboard</v>
+      </c>
+      <c r="I3">
+        <f>_xlfn.XLOOKUP(C3,tbl_product[product_id],tbl_product[price])</f>
+        <v>120</v>
+      </c>
+      <c r="J3">
+        <f>_xlfn.XLOOKUP(C3,tbl_product[product_id],tbl_product[category_id])</f>
+        <v>3</v>
+      </c>
+      <c r="L3" t="str">
+        <f>VLOOKUP(C3,Products!A:D,2,FALSE)</f>
+        <v>Mechanical Keyboard</v>
+      </c>
+      <c r="M3">
+        <f>VLOOKUP(C3,Products!A:D,4,FALSE)</f>
+        <v>120</v>
+      </c>
+      <c r="N3">
+        <f>VLOOKUP(C3,Products!A:D,3,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="P3" t="str">
+        <f>INDEX(Products!B:B,MATCH(C3,Products!A:A,0))</f>
+        <v>Mechanical Keyboard</v>
+      </c>
+      <c r="Q3">
+        <f>INDEX(Products!D:D,MATCH(C3,Products!A:A,0))</f>
+        <v>120</v>
+      </c>
+      <c r="R3">
+        <f>INDEX(Products!C:C,MATCH(C3,Products!A:A,0))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2591,11 +3169,55 @@
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="E4" s="23">
+        <v>999</v>
+      </c>
+      <c r="F4">
+        <f>_xlfn.XLOOKUP(B4,Orders!A:A,Orders!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <f>D4*E4</f>
+        <v>999</v>
+      </c>
+      <c r="H4" t="str">
+        <f>_xlfn.XLOOKUP(C4,tbl_product[product_id],tbl_product[product_name])</f>
+        <v>iPhone 15</v>
+      </c>
+      <c r="I4">
+        <f>_xlfn.XLOOKUP(C4,tbl_product[product_id],tbl_product[price])</f>
+        <v>990</v>
+      </c>
+      <c r="J4">
+        <f>_xlfn.XLOOKUP(C4,tbl_product[product_id],tbl_product[category_id])</f>
+        <v>2</v>
+      </c>
+      <c r="L4" t="str">
+        <f>VLOOKUP(C4,Products!A:D,2,FALSE)</f>
+        <v>iPhone 15</v>
+      </c>
+      <c r="M4">
+        <f>VLOOKUP(C4,Products!A:D,4,FALSE)</f>
+        <v>990</v>
+      </c>
+      <c r="N4">
+        <f>VLOOKUP(C4,Products!A:D,3,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="P4" t="str">
+        <f>INDEX(Products!B:B,MATCH(C4,Products!A:A,0))</f>
+        <v>iPhone 15</v>
+      </c>
+      <c r="Q4">
+        <f>INDEX(Products!D:D,MATCH(C4,Products!A:A,0))</f>
+        <v>990</v>
+      </c>
+      <c r="R4">
+        <f>INDEX(Products!C:C,MATCH(C4,Products!A:A,0))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2608,11 +3230,55 @@
       <c r="D5">
         <v>2</v>
       </c>
-      <c r="E5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="E5" s="23">
+        <v>280</v>
+      </c>
+      <c r="F5">
+        <f>_xlfn.XLOOKUP(B5,Orders!A:A,Orders!B:B)</f>
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <f t="shared" ref="G3:G10" si="0">D5*E5</f>
+        <v>560</v>
+      </c>
+      <c r="H5" t="str">
+        <f>_xlfn.XLOOKUP(C5,tbl_product[product_id],tbl_product[product_name])</f>
+        <v>Dell 27 Monitor</v>
+      </c>
+      <c r="I5">
+        <f>_xlfn.XLOOKUP(C5,tbl_product[product_id],tbl_product[price])</f>
+        <v>280</v>
+      </c>
+      <c r="J5">
+        <f>_xlfn.XLOOKUP(C5,tbl_product[product_id],tbl_product[category_id])</f>
+        <v>4</v>
+      </c>
+      <c r="L5" t="str">
+        <f>VLOOKUP(C5,Products!A:D,2,FALSE)</f>
+        <v>Dell 27 Monitor</v>
+      </c>
+      <c r="M5">
+        <f>VLOOKUP(C5,Products!A:D,4,FALSE)</f>
+        <v>280</v>
+      </c>
+      <c r="N5">
+        <f>VLOOKUP(C5,Products!A:D,3,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="P5" t="str">
+        <f>INDEX(Products!B:B,MATCH(C5,Products!A:A,0))</f>
+        <v>Dell 27 Monitor</v>
+      </c>
+      <c r="Q5">
+        <f>INDEX(Products!D:D,MATCH(C5,Products!A:A,0))</f>
+        <v>280</v>
+      </c>
+      <c r="R5">
+        <f>INDEX(Products!C:C,MATCH(C5,Products!A:A,0))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2625,11 +3291,55 @@
       <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="E6" s="23">
+        <v>950</v>
+      </c>
+      <c r="F6">
+        <f>_xlfn.XLOOKUP(B6,Orders!A:A,Orders!B:B)</f>
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="H6" t="str">
+        <f>_xlfn.XLOOKUP(C6,tbl_product[product_id],tbl_product[product_name])</f>
+        <v>Samsung S24</v>
+      </c>
+      <c r="I6">
+        <f>_xlfn.XLOOKUP(C6,tbl_product[product_id],tbl_product[price])</f>
+        <v>950</v>
+      </c>
+      <c r="J6">
+        <f>_xlfn.XLOOKUP(C6,tbl_product[product_id],tbl_product[category_id])</f>
+        <v>2</v>
+      </c>
+      <c r="L6" t="str">
+        <f>VLOOKUP(C6,Products!A:D,2,FALSE)</f>
+        <v>Samsung S24</v>
+      </c>
+      <c r="M6">
+        <f>VLOOKUP(C6,Products!A:D,4,FALSE)</f>
+        <v>950</v>
+      </c>
+      <c r="N6">
+        <f>VLOOKUP(C6,Products!A:D,3,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="P6" t="str">
+        <f>INDEX(Products!B:B,MATCH(C6,Products!A:A,0))</f>
+        <v>Samsung S24</v>
+      </c>
+      <c r="Q6">
+        <f>INDEX(Products!D:D,MATCH(C6,Products!A:A,0))</f>
+        <v>950</v>
+      </c>
+      <c r="R6">
+        <f>INDEX(Products!C:C,MATCH(C6,Products!A:A,0))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2642,11 +3352,55 @@
       <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="E7" s="23">
+        <v>550</v>
+      </c>
+      <c r="F7">
+        <f>_xlfn.XLOOKUP(B7,Orders!A:A,Orders!B:B)</f>
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>550</v>
+      </c>
+      <c r="H7" t="str">
+        <f>_xlfn.XLOOKUP(C7,tbl_product[product_id],tbl_product[product_name])</f>
+        <v>PlayStation 5</v>
+      </c>
+      <c r="I7">
+        <f>_xlfn.XLOOKUP(C7,tbl_product[product_id],tbl_product[price])</f>
+        <v>550</v>
+      </c>
+      <c r="J7">
+        <f>_xlfn.XLOOKUP(C7,tbl_product[product_id],tbl_product[category_id])</f>
+        <v>5</v>
+      </c>
+      <c r="L7" t="str">
+        <f>VLOOKUP(C7,Products!A:D,2,FALSE)</f>
+        <v>PlayStation 5</v>
+      </c>
+      <c r="M7">
+        <f>VLOOKUP(C7,Products!A:D,4,FALSE)</f>
+        <v>550</v>
+      </c>
+      <c r="N7">
+        <f>VLOOKUP(C7,Products!A:D,3,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="P7" t="str">
+        <f>INDEX(Products!B:B,MATCH(C7,Products!A:A,0))</f>
+        <v>PlayStation 5</v>
+      </c>
+      <c r="Q7">
+        <f>INDEX(Products!D:D,MATCH(C7,Products!A:A,0))</f>
+        <v>550</v>
+      </c>
+      <c r="R7">
+        <f>INDEX(Products!C:C,MATCH(C7,Products!A:A,0))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2659,11 +3413,55 @@
       <c r="D8">
         <v>2</v>
       </c>
-      <c r="E8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="E8" s="23">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <f>_xlfn.XLOOKUP(B8,Orders!A:A,Orders!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H8" t="str">
+        <f>_xlfn.XLOOKUP(C8,tbl_product[product_id],tbl_product[product_name])</f>
+        <v>Wireless Mouse</v>
+      </c>
+      <c r="I8">
+        <f>_xlfn.XLOOKUP(C8,tbl_product[product_id],tbl_product[price])</f>
+        <v>50</v>
+      </c>
+      <c r="J8">
+        <f>_xlfn.XLOOKUP(C8,tbl_product[product_id],tbl_product[category_id])</f>
+        <v>3</v>
+      </c>
+      <c r="L8" t="str">
+        <f>VLOOKUP(C8,Products!A:D,2,FALSE)</f>
+        <v>Wireless Mouse</v>
+      </c>
+      <c r="M8">
+        <f>VLOOKUP(C8,Products!A:D,4,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="N8">
+        <f>VLOOKUP(C8,Products!A:D,3,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="P8" t="str">
+        <f>INDEX(Products!B:B,MATCH(C8,Products!A:A,0))</f>
+        <v>Wireless Mouse</v>
+      </c>
+      <c r="Q8">
+        <f>INDEX(Products!D:D,MATCH(C8,Products!A:A,0))</f>
+        <v>50</v>
+      </c>
+      <c r="R8">
+        <f>INDEX(Products!C:C,MATCH(C8,Products!A:A,0))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2676,11 +3474,55 @@
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="E9" s="23">
+        <v>1100</v>
+      </c>
+      <c r="F9">
+        <f>_xlfn.XLOOKUP(B9,Orders!A:A,Orders!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>1100</v>
+      </c>
+      <c r="H9" t="str">
+        <f>_xlfn.XLOOKUP(C9,tbl_product[product_id],tbl_product[product_name])</f>
+        <v>ThinkPad T14</v>
+      </c>
+      <c r="I9">
+        <f>_xlfn.XLOOKUP(C9,tbl_product[product_id],tbl_product[price])</f>
+        <v>1100</v>
+      </c>
+      <c r="J9">
+        <f>_xlfn.XLOOKUP(C9,tbl_product[product_id],tbl_product[category_id])</f>
+        <v>1</v>
+      </c>
+      <c r="L9" t="str">
+        <f>VLOOKUP(C9,Products!A:D,2,FALSE)</f>
+        <v>ThinkPad T14</v>
+      </c>
+      <c r="M9">
+        <f>VLOOKUP(C9,Products!A:D,4,FALSE)</f>
+        <v>1100</v>
+      </c>
+      <c r="N9">
+        <f>VLOOKUP(C9,Products!A:D,3,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="P9" t="str">
+        <f>INDEX(Products!B:B,MATCH(C9,Products!A:A,0))</f>
+        <v>ThinkPad T14</v>
+      </c>
+      <c r="Q9">
+        <f>INDEX(Products!D:D,MATCH(C9,Products!A:A,0))</f>
+        <v>1100</v>
+      </c>
+      <c r="R9">
+        <f>INDEX(Products!C:C,MATCH(C9,Products!A:A,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2693,8 +3535,226 @@
       <c r="D10">
         <v>1</v>
       </c>
-      <c r="E10" t="s">
-        <v>106</v>
+      <c r="E10" s="30">
+        <v>530</v>
+      </c>
+      <c r="F10">
+        <f>_xlfn.XLOOKUP(B10,Orders!A:A,Orders!B:B)</f>
+        <v>6</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>530</v>
+      </c>
+      <c r="H10" t="str">
+        <f>_xlfn.XLOOKUP(C10,tbl_product[product_id],tbl_product[product_name])</f>
+        <v>Xbox Series X</v>
+      </c>
+      <c r="I10">
+        <f>_xlfn.XLOOKUP(C10,tbl_product[product_id],tbl_product[price])</f>
+        <v>530</v>
+      </c>
+      <c r="J10">
+        <f>_xlfn.XLOOKUP(C10,tbl_product[product_id],tbl_product[category_id])</f>
+        <v>5</v>
+      </c>
+      <c r="L10" t="str">
+        <f>VLOOKUP(C10,Products!A:D,2,FALSE)</f>
+        <v>Xbox Series X</v>
+      </c>
+      <c r="M10">
+        <f>VLOOKUP(C10,Products!A:D,4,FALSE)</f>
+        <v>530</v>
+      </c>
+      <c r="N10">
+        <f>VLOOKUP(C10,Products!A:D,3,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="P10" t="str">
+        <f>INDEX(Products!B:B,MATCH(C10,Products!A:A,0))</f>
+        <v>Xbox Series X</v>
+      </c>
+      <c r="Q10">
+        <f>INDEX(Products!D:D,MATCH(C10,Products!A:A,0))</f>
+        <v>530</v>
+      </c>
+      <c r="R10">
+        <f>INDEX(Products!C:C,MATCH(C10,Products!A:A,0))</f>
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FA86454-020B-46BA-96FB-07D4B32F2F86}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="1">
+        <v>45296</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="1">
+        <v>45303</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="1">
+        <v>45324</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="1">
+        <v>45340</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="1">
+        <v>45361</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="1">
+        <v>45376</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="1">
+        <v>45394</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="1">
+        <v>45410</v>
       </c>
     </row>
   </sheetData>
@@ -2705,218 +3765,45 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FA86454-020B-46BA-96FB-07D4B32F2F86}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B7E5F15-8FF1-4142-BD7B-00B7D5F5396F}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.75" customWidth="1"/>
-    <col min="2" max="2" width="10.25" customWidth="1"/>
-    <col min="3" max="3" width="17.75" customWidth="1"/>
-    <col min="4" max="4" width="16.5" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E2" s="1">
-        <v>45296</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E3" s="1">
-        <v>45303</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E4" s="1">
-        <v>45324</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" s="1">
-        <v>45340</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" s="1">
-        <v>45361</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7" t="s">
-        <v>112</v>
-      </c>
-      <c r="E7" s="1">
-        <v>45376</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E8" s="1">
-        <v>45394</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>111</v>
-      </c>
-      <c r="D9" t="s">
-        <v>112</v>
-      </c>
-      <c r="E9" s="1">
-        <v>45410</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B7E5F15-8FF1-4142-BD7B-00B7D5F5396F}">
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="9.625" customWidth="1"/>
-    <col min="5" max="5" width="9.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="30">
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="H1" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="I1" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="C1" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>3</v>
       </c>
@@ -2952,9 +3839,9 @@
         <v>Premium</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B3" s="25">
         <v>1200</v>
@@ -2973,9 +3860,9 @@
         <v>VIP</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="B4" s="25">
         <v>900</v>
@@ -2994,7 +3881,7 @@
         <v>Regular</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
         <v>0</v>
       </c>
@@ -3018,7 +3905,7 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B2:B5">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
